--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1591-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1591-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E09A5C7-4749-42BE-A0CD-9E07B70589E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6817F7C-8EC9-4873-B161-5970C1492166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{C356E8F1-0CA9-4837-8498-D30EE475C8F7}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{68839299-6E4C-4EA8-82C6-1AA9B60D0060}"/>
   </bookViews>
   <sheets>
     <sheet name="1591-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1520,20 +1520,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB1A1CF6-D57B-4B9D-B24E-22D12109A4D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B273F18-5147-4403-A57A-BFAD8598516E}">
   <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1561,7 +1561,7 @@
       <c r="Q1" s="33"/>
       <c r="R1" s="25"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1591,7 +1591,7 @@
       <c r="Q2" s="35"/>
       <c r="R2" s="36"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1687,7 +1687,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="40">
         <v>2026</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="42">
         <v>2025</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="40">
         <v>2024</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="42">
         <v>2023</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>2022</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
         <v>26</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="45"/>
       <c r="B21" s="22" t="s">
         <v>36</v>
@@ -2595,7 +2595,7 @@
       <c r="Q21" s="49"/>
       <c r="R21" s="49"/>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="42">
         <v>2021</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>2020</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="42">
         <v>2019</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>26</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2018</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="42">
         <v>2017</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2016</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="42">
         <v>2015</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2014</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="42">
         <v>2013</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2012</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="42">
         <v>2011</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="40">
         <v>2010</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="42" t="s">
         <v>45</v>
       </c>
